--- a/analysis/econometrics_outputs/contdid/Graficos/contracts/dose/contdid_cosine_weighted_dose_acrt.xlsx
+++ b/analysis/econometrics_outputs/contdid/Graficos/contracts/dose/contdid_cosine_weighted_dose_acrt.xlsx
@@ -488,10 +488,10 @@
         <v>-1510.43868720317</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>10230.4300798229</v>
+        <v>26322.5545738963</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -510,10 +510,10 @@
         <v>-1396.13919175418</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>10087.8265401477</v>
+        <v>24990.2478835963</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -532,10 +532,10 @@
         <v>-1314.33074889358</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>9984.54708255449</v>
+        <v>24035.4019026147</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -554,10 +554,10 @@
         <v>-1240.40391164952</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>9890.3013598226</v>
+        <v>23171.5926976242</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -576,10 +576,10 @@
         <v>-1139.95598663656</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>9760.77806543033</v>
+        <v>22118.6105160451</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -598,10 +598,10 @@
         <v>-1037.33280996603</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>9626.60159455793</v>
+        <v>21220.809511864</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -620,10 +620,10 @@
         <v>-997.966661892118</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>9574.60970738935</v>
+        <v>20875.7034529313</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -642,10 +642,10 @@
         <v>-948.647830569955</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>9509.04715990963</v>
+        <v>20442.7667446591</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -664,10 +664,10 @@
         <v>-885.57385895313</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>9424.48464773961</v>
+        <v>19888.1104320299</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -686,10 +686,10 @@
         <v>-831.866168602755</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>9351.82253349807</v>
+        <v>19337.9541276229</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -708,10 +708,10 @@
         <v>-760.2472480428</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>9253.9448340315</v>
+        <v>18592.9961252321</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -730,10 +730,10 @@
         <v>-686.948312535021</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>9152.54936915542</v>
+        <v>17829.0455922987</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -752,10 +752,10 @@
         <v>-421.447778866979</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>8773.74618095273</v>
+        <v>15352.1564540025</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -774,10 +774,10 @@
         <v>-298.796633458323</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>8591.80153650849</v>
+        <v>14201.3527714769</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -796,10 +796,10 @@
         <v>-193.864670264507</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>8432.09538903201</v>
+        <v>13211.4231935441</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -818,10 +818,10 @@
         <v>-17.8896305967076</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>8073.02364170901</v>
+        <v>11617.3476475946</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -840,10 +840,10 @@
         <v>130.420855423623</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>7909.8215952416</v>
+        <v>10753.1973262793</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -862,10 +862,10 @@
         <v>196.378171306209</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>7797.15081076193</v>
+        <v>9936.75209268711</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -884,10 +884,10 @@
         <v>300.091053571213</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>7614.52613824192</v>
+        <v>9509.70015269536</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -906,10 +906,10 @@
         <v>376.325897360528</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>7475.46813978586</v>
+        <v>9414.55009825974</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -928,10 +928,10 @@
         <v>444.805462925903</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>7346.56996542101</v>
+        <v>8997.36034186677</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -950,10 +950,10 @@
         <v>489.223195662919</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>7260.70661605077</v>
+        <v>8436.54202630194</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -972,10 +972,10 @@
         <v>640.011829902459</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>6953.3972871721</v>
+        <v>7060.04330258153</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -994,10 +994,10 @@
         <v>730.204861366401</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>6755.05733498738</v>
+        <v>6070.11892139748</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1016,10 +1016,10 @@
         <v>816.11110078301</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>6552.70267157426</v>
+        <v>4800.87691816861</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -1038,10 +1038,10 @@
         <v>835.232604588055</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>6505.48683287438</v>
+        <v>4628.4174713284</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1060,10 +1060,10 @@
         <v>877.770644031263</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>6397.08146775262</v>
+        <v>4454.88319768914</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1082,10 +1082,10 @@
         <v>891.404409531703</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>6361.2534423366</v>
+        <v>4278.23173290622</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1104,10 +1104,10 @@
         <v>962.069305884367</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>6165.43840740538</v>
+        <v>4153.22683733105</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1126,10 +1126,10 @@
         <v>985.982416346126</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>6094.60565456422</v>
+        <v>4206.9466467917</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -1148,10 +1148,10 @@
         <v>1035.15699443815</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>5939.5153820448</v>
+        <v>4317.36819111985</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1170,10 +1170,10 @@
         <v>1060.27350410281</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>5854.24634814686</v>
+        <v>4153.26918034822</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1192,10 +1192,10 @@
         <v>1130.45539624441</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>5583.76669522522</v>
+        <v>4012.50817899861</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -1214,10 +1214,10 @@
         <v>1179.98651116273</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>5343.09952658326</v>
+        <v>4232.33739771035</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -1236,10 +1236,10 @@
         <v>1202.55581389901</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>5204.73425127659</v>
+        <v>4420.06185925789</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -1258,10 +1258,10 @@
         <v>1234.46994034494</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>4631.60348089097</v>
+        <v>5257.46099926281</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1280,10 +1280,10 @@
         <v>1244.39864711663</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>4094.24066417776</v>
+        <v>5951.19361023719</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -1302,10 +1302,10 @@
         <v>1242.63304954713</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>3748.27630365151</v>
+        <v>6323.95699513399</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -1324,10 +1324,10 @@
         <v>1239.09766826985</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>3605.36230236673</v>
+        <v>6418.04469210302</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -1346,10 +1346,10 @@
         <v>1192.03597241326</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>3037.88452775866</v>
+        <v>6335.34925099208</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -1368,10 +1368,10 @@
         <v>1153.78678906954</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>2879.94555423202</v>
+        <v>6193.45985492344</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -1390,10 +1390,10 @@
         <v>1060.4084180542</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>2609.13630502611</v>
+        <v>5855.12959003349</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -1412,10 +1412,10 @@
         <v>993.943627967458</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>2410.95999187957</v>
+        <v>5475.8295693399</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -1434,10 +1434,10 @@
         <v>974.792343030865</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>2352.91503911717</v>
+        <v>5367.97105993774</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -1456,10 +1456,10 @@
         <v>934.416586810261</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>2229.02932490769</v>
+        <v>5126.46673562532</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -1478,10 +1478,10 @@
         <v>804.428751943367</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>1813.90900812313</v>
+        <v>4264.20039886379</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -1500,10 +1500,10 @@
         <v>718.705618277351</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>1580.31421697779</v>
+        <v>3822.49998952281</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -1522,10 +1522,10 @@
         <v>688.594346882642</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>1500.32734421285</v>
+        <v>3640.23796706728</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -1544,10 +1544,10 @@
         <v>668.492533157919</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>1445.4173446699</v>
+        <v>3529.78871712239</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -1566,10 +1566,10 @@
         <v>659.724900886977</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>1421.05849778655</v>
+        <v>3481.15646070658</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -1588,10 +1588,10 @@
         <v>534.387700478576</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>1038.26842311581</v>
+        <v>2790.43415703296</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -1610,10 +1610,10 @@
         <v>419.726079250292</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>418.474599101367</v>
+        <v>1914.47893378297</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -1632,10 +1632,10 @@
         <v>400.952656821685</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>281.53813231322</v>
+        <v>1652.51256601344</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -1654,10 +1654,10 @@
         <v>348.918423571711</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>162.051436126468</v>
+        <v>1217.42379126707</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -1676,10 +1676,10 @@
         <v>323.262128614589</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>368.316992095115</v>
+        <v>1010.31586232793</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -1698,10 +1698,10 @@
         <v>321.376382466</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>369.042581633205</v>
+        <v>991.199085544081</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -1720,10 +1720,10 @@
         <v>321.376382466</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>369.042581633205</v>
+        <v>991.199085544081</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -1742,10 +1742,10 @@
         <v>313.054308185477</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>371.474587588979</v>
+        <v>965.055936472206</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -1764,10 +1764,10 @@
         <v>310.366671140348</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>371.864749305871</v>
+        <v>937.343984219924</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -1786,10 +1786,10 @@
         <v>301.273438243426</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>505.847364898931</v>
+        <v>798.616964870232</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
@@ -1808,10 +1808,10 @@
         <v>300.527453124074</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>534.664145074825</v>
+        <v>821.96652674245</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -1830,10 +1830,10 @@
         <v>308.753468820671</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>836.519939158466</v>
+        <v>845.988296266404</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -1852,10 +1852,10 @@
         <v>313.27116831025</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>880.44872838435</v>
+        <v>892.325089346247</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -1874,10 +1874,10 @@
         <v>334.063327536364</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>1008.00070309279</v>
+        <v>904.422051263298</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -1896,10 +1896,10 @@
         <v>361.404335684375</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>1105.50871071256</v>
+        <v>1002.06845446769</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -1918,10 +1918,10 @@
         <v>412.215639231237</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>1209.82286740817</v>
+        <v>1167.72336947742</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -1940,10 +1940,10 @@
         <v>459.323386411907</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>1264.1281387993</v>
+        <v>1269.08350926884</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
@@ -1962,10 +1962,10 @@
         <v>520.700832301132</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>1301.81625850052</v>
+        <v>1333.22618328394</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
@@ -1984,10 +1984,10 @@
         <v>650.418724256723</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>1424.98616903353</v>
+        <v>1471.42664755407</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
@@ -2006,10 +2006,10 @@
         <v>766.431084962801</v>
       </c>
       <c r="F75" s="1" t="n">
-        <v>1524.60663762035</v>
+        <v>1568.91525985888</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
@@ -2028,10 +2028,10 @@
         <v>966.452447936663</v>
       </c>
       <c r="F76" s="1" t="n">
-        <v>1631.81099520249</v>
+        <v>1639.6139621234</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
@@ -2050,10 +2050,10 @@
         <v>1100.34752963477</v>
       </c>
       <c r="F77" s="1" t="n">
-        <v>1507.63249640994</v>
+        <v>1517.4462654208</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -2072,10 +2072,10 @@
         <v>1273.46954451395</v>
       </c>
       <c r="F78" s="1" t="n">
-        <v>1313.01370531551</v>
+        <v>1441.18478580906</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
@@ -2094,10 +2094,10 @@
         <v>1367.47551035034</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>1195.8171026579</v>
+        <v>1418.76023774844</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
@@ -2116,10 +2116,10 @@
         <v>1442.11749154165</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>1097.91405421341</v>
+        <v>1445.22715248882</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
@@ -2138,10 +2138,10 @@
         <v>1515.44235426952</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>997.997904602749</v>
+        <v>1489.5559140196</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
@@ -2160,10 +2160,10 @@
         <v>1607.49568918475</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>867.819025365351</v>
+        <v>1438.50513522636</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
@@ -2182,10 +2182,10 @@
         <v>1688.6656014187</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>749.058683228853</v>
+        <v>1468.32856111659</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
@@ -2204,10 +2204,10 @@
         <v>1816.56514737023</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>555.165831013385</v>
+        <v>1380.1884325816</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
@@ -2226,10 +2226,10 @@
         <v>2365.3304915586</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>517.282977214638</v>
+        <v>1349.99214550577</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
@@ -2248,10 +2248,10 @@
         <v>2507.67314279429</v>
       </c>
       <c r="F86" s="1" t="n">
-        <v>724.001729488408</v>
+        <v>1405.18877450745</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
@@ -2270,10 +2270,10 @@
         <v>3278.686290203</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>2038.85007386353</v>
+        <v>2423.2202893826</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
@@ -2292,10 +2292,10 @@
         <v>3769.40939851503</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>3007.55493199644</v>
+        <v>2825.22299667993</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
@@ -2314,10 +2314,10 @@
         <v>3814.00359410184</v>
       </c>
       <c r="F89" s="1" t="n">
-        <v>3097.24725632201</v>
+        <v>2920.14471953073</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -2336,10 +2336,10 @@
         <v>4260.97298800619</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>4009.5084042437</v>
+        <v>3591.23853848163</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
@@ -2358,10 +2358,10 @@
         <v>4767.25611996883</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>4887.92316799939</v>
+        <v>3991.09508445686</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
@@ -2380,10 +2380,10 @@
         <v>5506.21721480551</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>5433.58679491767</v>
+        <v>4474.18161950328</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -2402,10 +2402,10 @@
         <v>5537.22967015151</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>5466.79327498817</v>
+        <v>4494.32663092237</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -2424,10 +2424,10 @@
         <v>6756.74430300773</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>6769.80764410718</v>
+        <v>6129.18390348991</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -2446,10 +2446,10 @@
         <v>8131.52134754841</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>8233.44556899836</v>
+        <v>8331.30390862385</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>11.7477881414541</v>
+        <v>2.46606159799714</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
